--- a/34th_Backgammon-championships_1a_output.xlsx
+++ b/34th_Backgammon-championships_1a_output.xlsx
@@ -1135,7 +1135,7 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -1226,7 +1226,7 @@
         <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5" t="n">
         <v>9</v>
@@ -1467,7 +1467,7 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
         <v>9</v>
@@ -1498,7 +1498,7 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1559,7 +1559,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -1632,7 +1632,7 @@
         <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -1647,7 +1647,7 @@
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
         <v>2</v>
@@ -1699,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
